--- a/Data/Building/MeetingRoomOne.Temperature.xlsx
+++ b/Data/Building/MeetingRoomOne.Temperature.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H231"/>
+  <dimension ref="A1:I217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>actionSource</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>violationLabel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -487,7 +492,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1709235914</v>
+        <v>1711829099</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -501,6 +506,7 @@
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -519,7 +525,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1709261221</v>
+        <v>1711852487</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -533,6 +539,11 @@
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -551,7 +562,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1709264483</v>
+        <v>1711855614</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -565,6 +576,7 @@
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -583,7 +595,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1709270736</v>
+        <v>1711859912</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -593,10 +605,11 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Temperature.state: ExcessivelyCold</t>
+          <t>MeetingRoomOne.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -615,7 +628,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1709274021</v>
+        <v>1711870314</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -625,10 +638,11 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Temperature.state: Cold</t>
+          <t>MeetingRoomOne.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -647,7 +661,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1709279907</v>
+        <v>1711871607</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -661,6 +675,7 @@
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -679,7 +694,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1709230280</v>
+        <v>1711872019</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -693,6 +708,7 @@
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -711,7 +727,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1709241147</v>
+        <v>1711872970</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -725,6 +741,11 @@
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -743,7 +764,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1709259946</v>
+        <v>1711876784</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -757,6 +778,7 @@
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -775,7 +797,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1709270291</v>
+        <v>1711901195</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -789,6 +811,11 @@
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -807,7 +834,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1709336524</v>
+        <v>1711907606</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -821,6 +848,7 @@
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -839,7 +867,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1709337368</v>
+        <v>1711908445</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -853,6 +881,11 @@
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -871,7 +904,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1709343470</v>
+        <v>1711918271</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -885,6 +918,7 @@
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -903,7 +937,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1709354020</v>
+        <v>1711919130</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -913,10 +947,15 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Temperature.state: Comfortable</t>
+          <t>MeetingRoomOne.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -935,7 +974,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1709402403</v>
+        <v>1711928278</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -949,6 +988,7 @@
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -967,7 +1007,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1709411723</v>
+        <v>1711932735</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -977,10 +1017,11 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Temperature.state: ExcessivelyCold</t>
+          <t>MeetingRoomOne.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -999,7 +1040,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1709427983</v>
+        <v>1711936545</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1009,10 +1050,11 @@
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Temperature.state: Cold</t>
+          <t>MeetingRoomOne.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1031,7 +1073,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1709428863</v>
+        <v>1711945958</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1041,10 +1083,15 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Temperature.state: ExcessivelyCold</t>
+          <t>MeetingRoomOne.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1063,7 +1110,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1709433344</v>
+        <v>1711951540</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1073,10 +1120,11 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Temperature.state: Cold</t>
+          <t>MeetingRoomOne.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1095,7 +1143,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1709441988</v>
+        <v>1711990873</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1109,6 +1157,7 @@
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1127,7 +1176,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1709489030</v>
+        <v>1711997884</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1141,6 +1190,7 @@
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1159,7 +1209,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1709498183</v>
+        <v>1712007164</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1173,6 +1223,11 @@
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1191,7 +1246,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1709518190</v>
+        <v>1712025554</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1205,6 +1260,7 @@
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1223,7 +1279,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1709588365</v>
+        <v>1712027895</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1237,6 +1293,11 @@
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1255,7 +1316,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1709602381</v>
+        <v>1712032616</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1269,6 +1330,7 @@
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1287,7 +1349,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1709603667</v>
+        <v>1712096575</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1301,6 +1363,11 @@
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1319,7 +1386,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1709608464</v>
+        <v>1712106930</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1333,6 +1400,7 @@
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1351,7 +1419,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1709613497</v>
+        <v>1712111176</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1365,6 +1433,7 @@
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1383,7 +1452,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1709617959</v>
+        <v>1712113921</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1397,6 +1466,7 @@
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1415,7 +1485,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1709618786</v>
+        <v>1712114731</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1429,6 +1499,11 @@
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1447,7 +1522,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1709623854</v>
+        <v>1712117916</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1461,6 +1536,7 @@
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1479,7 +1555,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1709624817</v>
+        <v>1712122373</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1489,10 +1565,11 @@
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Temperature.state: ExcessivelyCold</t>
+          <t>MeetingRoomOne.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1511,7 +1588,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1709687338</v>
+        <v>1712167674</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1525,6 +1602,7 @@
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1543,7 +1621,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1709688256</v>
+        <v>1712177189</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1557,6 +1635,11 @@
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1575,7 +1658,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1709693404</v>
+        <v>1712189329</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1589,6 +1672,7 @@
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1607,7 +1691,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1709694335</v>
+        <v>1712193164</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1617,10 +1701,11 @@
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Temperature.state: ExcessivelyCold</t>
+          <t>MeetingRoomOne.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1639,7 +1724,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1709698631</v>
+        <v>1712196714</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1653,6 +1738,7 @@
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1671,7 +1757,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1709699618</v>
+        <v>1712197589</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1685,6 +1771,11 @@
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1703,7 +1794,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1709703070</v>
+        <v>1712198713</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1717,6 +1808,7 @@
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1735,7 +1827,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1709704113</v>
+        <v>1712198956</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1745,10 +1837,11 @@
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Temperature.state: ExcessivelyCold</t>
+          <t>MeetingRoomOne.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1767,7 +1860,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1709707490</v>
+        <v>1712199301</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1777,10 +1870,11 @@
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Temperature.state: Cold</t>
+          <t>MeetingRoomOne.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1799,7 +1893,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1709708495</v>
+        <v>1712200091</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1809,10 +1903,15 @@
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Temperature.state: ExcessivelyCold</t>
+          <t>MeetingRoomOne.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1831,7 +1930,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1709712840</v>
+        <v>1712208969</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1841,10 +1940,11 @@
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Temperature.state: Cold</t>
+          <t>MeetingRoomOne.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1863,7 +1963,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1709713772</v>
+        <v>1712216751</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1873,10 +1973,11 @@
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Temperature.state: ExcessivelyCold</t>
+          <t>MeetingRoomOne.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1895,7 +1996,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1709719420</v>
+        <v>1712254782</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1909,6 +2010,7 @@
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1927,7 +2029,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1709741414</v>
+        <v>1712264212</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1941,6 +2043,11 @@
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1959,7 +2066,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1709774905</v>
+        <v>1712279699</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1973,6 +2080,7 @@
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1991,7 +2099,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1709775748</v>
+        <v>1712280641</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2005,6 +2113,11 @@
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2023,7 +2136,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1709782280</v>
+        <v>1712282709</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2037,6 +2150,7 @@
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2055,7 +2169,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1709783223</v>
+        <v>1712282950</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2065,10 +2179,11 @@
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Temperature.state: ExcessivelyCold</t>
+          <t>MeetingRoomOne.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2087,7 +2202,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1709788154</v>
+        <v>1712283359</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2097,10 +2212,11 @@
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Temperature.state: Cold</t>
+          <t>MeetingRoomOne.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2119,7 +2235,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1709789093</v>
+        <v>1712284193</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2129,10 +2245,11 @@
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Temperature.state: ExcessivelyCold</t>
+          <t>MeetingRoomOne.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2151,7 +2268,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1709794200</v>
+        <v>1712284595</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2165,6 +2282,7 @@
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2183,7 +2301,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1709795128</v>
+        <v>1712285448</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2197,6 +2315,11 @@
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2215,7 +2338,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1709827462</v>
+        <v>1712290403</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2229,6 +2352,7 @@
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2247,7 +2371,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1709828300</v>
+        <v>1712353509</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2261,6 +2385,11 @@
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2279,7 +2408,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1709858001</v>
+        <v>1712367861</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2293,6 +2422,7 @@
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2311,7 +2441,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1709858935</v>
+        <v>1712376363</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2321,10 +2451,11 @@
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Temperature.state: ExcessivelyCold</t>
+          <t>MeetingRoomOne.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2343,7 +2474,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1709863798</v>
+        <v>1712385678</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2353,10 +2484,11 @@
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Temperature.state: Cold</t>
+          <t>MeetingRoomOne.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2375,7 +2507,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1709864785</v>
+        <v>1712398609</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2385,10 +2517,11 @@
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Temperature.state: ExcessivelyCold</t>
+          <t>MeetingRoomOne.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2407,7 +2540,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1709868134</v>
+        <v>1712425881</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2421,6 +2554,7 @@
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2439,7 +2573,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1709873602</v>
+        <v>1712435166</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2449,10 +2583,15 @@
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Temperature.state: Comfortable</t>
+          <t>MeetingRoomOne.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2471,7 +2610,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1709919518</v>
+        <v>1712456268</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2485,6 +2624,7 @@
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2503,7 +2643,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1709928905</v>
+        <v>1712464327</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2513,10 +2653,11 @@
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Temperature.state: ExcessivelyCold</t>
+          <t>MeetingRoomOne.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2535,7 +2676,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1709946750</v>
+        <v>1712473584</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -2545,10 +2686,11 @@
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Temperature.state: Cold</t>
+          <t>MeetingRoomOne.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2567,7 +2709,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1709947924</v>
+        <v>1712485850</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -2577,10 +2719,11 @@
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Temperature.state: ExcessivelyCold</t>
+          <t>MeetingRoomOne.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2599,7 +2742,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1709952005</v>
+        <v>1712512406</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2613,6 +2756,7 @@
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2631,7 +2775,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1709960805</v>
+        <v>1712521620</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2645,6 +2789,11 @@
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2663,7 +2812,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1709966518</v>
+        <v>1712534936</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2677,6 +2826,7 @@
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2695,7 +2845,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1710000447</v>
+        <v>1712535215</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -2705,10 +2855,11 @@
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Temperature.state: ExcessivelyCold</t>
+          <t>MeetingRoomOne.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2727,7 +2878,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1710033544</v>
+        <v>1712552403</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -2737,10 +2888,11 @@
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Temperature.state: Cold</t>
+          <t>MeetingRoomOne.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2759,7 +2911,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1710034402</v>
+        <v>1712561819</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -2769,10 +2921,11 @@
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Temperature.state: ExcessivelyCold</t>
+          <t>MeetingRoomOne.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2791,7 +2944,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1710039300</v>
+        <v>1712597839</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -2805,6 +2958,7 @@
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2823,7 +2977,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1710040249</v>
+        <v>1712606934</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -2837,6 +2991,11 @@
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2855,7 +3014,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1710043737</v>
+        <v>1712625029</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -2869,6 +3028,7 @@
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2887,7 +3047,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1710048576</v>
+        <v>1712627949</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -2897,10 +3057,15 @@
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Temperature.state: Comfortable</t>
+          <t>MeetingRoomOne.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2919,7 +3084,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1710093726</v>
+        <v>1712630185</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -2933,6 +3098,7 @@
         </is>
       </c>
       <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2951,7 +3117,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1710103174</v>
+        <v>1712631732</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -2961,10 +3127,11 @@
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Temperature.state: ExcessivelyCold</t>
+          <t>MeetingRoomOne.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2983,7 +3150,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>1710123506</v>
+        <v>1712632082</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -2993,10 +3160,11 @@
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Temperature.state: Cold</t>
+          <t>MeetingRoomOne.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3015,7 +3183,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>1710130454</v>
+        <v>1712681912</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -3029,6 +3197,7 @@
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3047,7 +3216,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1710181927</v>
+        <v>1712689689</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -3061,6 +3230,7 @@
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3079,7 +3249,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>1710191656</v>
+        <v>1712698810</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -3093,6 +3263,11 @@
         </is>
       </c>
       <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3111,7 +3286,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1710206937</v>
+        <v>1712708070</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -3125,6 +3300,7 @@
         </is>
       </c>
       <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3143,7 +3319,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>1710212840</v>
+        <v>1712708316</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -3153,10 +3329,11 @@
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Temperature.state: ExcessivelyCold</t>
+          <t>MeetingRoomOne.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3175,7 +3352,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1710216093</v>
+        <v>1712708775</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -3185,10 +3362,11 @@
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Temperature.state: Cold</t>
+          <t>MeetingRoomOne.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3207,7 +3385,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>1710221107</v>
+        <v>1712712976</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -3221,6 +3399,7 @@
         </is>
       </c>
       <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3239,7 +3418,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>1710266360</v>
+        <v>1712767899</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -3253,6 +3432,7 @@
         </is>
       </c>
       <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3271,7 +3451,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>1710276024</v>
+        <v>1712778723</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -3285,6 +3465,11 @@
         </is>
       </c>
       <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3303,7 +3488,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>1710293643</v>
+        <v>1712800317</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -3317,6 +3502,7 @@
         </is>
       </c>
       <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3335,7 +3521,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>1710301750</v>
+        <v>1712816623</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -3349,6 +3535,7 @@
         </is>
       </c>
       <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3367,7 +3554,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>1710311020</v>
+        <v>1712856898</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -3377,10 +3564,11 @@
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Temperature.state: Warm</t>
+          <t>MeetingRoomOne.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3399,7 +3587,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>1710323449</v>
+        <v>1712865983</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -3409,10 +3597,15 @@
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Temperature.state: Comfortable</t>
+          <t>MeetingRoomOne.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3431,7 +3624,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>1710353698</v>
+        <v>1712884632</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -3445,6 +3638,7 @@
         </is>
       </c>
       <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3463,7 +3657,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>1710362953</v>
+        <v>1712886714</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -3477,6 +3671,11 @@
         </is>
       </c>
       <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3495,7 +3694,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>1710386469</v>
+        <v>1712888725</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -3509,6 +3708,7 @@
         </is>
       </c>
       <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3527,7 +3727,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>1710395914</v>
+        <v>1712901894</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -3541,6 +3741,7 @@
         </is>
       </c>
       <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3559,7 +3760,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>1710437706</v>
+        <v>1712943300</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -3573,6 +3774,7 @@
         </is>
       </c>
       <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3591,7 +3793,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>1710446885</v>
+        <v>1712952822</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -3605,6 +3807,11 @@
         </is>
       </c>
       <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3623,7 +3830,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>1710466251</v>
+        <v>1712971965</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -3637,6 +3844,7 @@
         </is>
       </c>
       <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3655,7 +3863,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>1710470374</v>
+        <v>1712980201</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -3665,10 +3873,11 @@
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Temperature.state: ExcessivelyCold</t>
+          <t>MeetingRoomOne.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3687,7 +3896,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>1710473692</v>
+        <v>1712989398</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -3697,10 +3906,11 @@
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Temperature.state: Cold</t>
+          <t>MeetingRoomOne.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3719,7 +3929,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>1710478503</v>
+        <v>1712999777</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -3733,6 +3943,7 @@
         </is>
       </c>
       <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3751,7 +3962,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>1710524634</v>
+        <v>1713030570</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -3765,6 +3976,7 @@
         </is>
       </c>
       <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3783,7 +3995,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1710534257</v>
+        <v>1713039944</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -3797,6 +4009,11 @@
         </is>
       </c>
       <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3815,7 +4032,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>1710551008</v>
+        <v>1713060140</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -3829,6 +4046,7 @@
         </is>
       </c>
       <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3847,7 +4065,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>1710558673</v>
+        <v>1713068777</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -3857,10 +4075,11 @@
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Temperature.state: ExcessivelyCold</t>
+          <t>MeetingRoomOne.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3879,7 +4098,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>1710561953</v>
+        <v>1713078163</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -3889,10 +4108,11 @@
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Temperature.state: Cold</t>
+          <t>MeetingRoomOne.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3911,7 +4131,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>1710568143</v>
+        <v>1713088572</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -3925,6 +4145,7 @@
         </is>
       </c>
       <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3943,7 +4164,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>1710610800</v>
+        <v>1713118447</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -3957,6 +4178,7 @@
         </is>
       </c>
       <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3975,7 +4197,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>1710620234</v>
+        <v>1713128055</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -3989,6 +4211,11 @@
         </is>
       </c>
       <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4007,7 +4234,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>1710640286</v>
+        <v>1713146040</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -4021,6 +4248,7 @@
         </is>
       </c>
       <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4039,7 +4267,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>1710641170</v>
+        <v>1713149374</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -4049,10 +4277,11 @@
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Temperature.state: ExcessivelyCold</t>
+          <t>MeetingRoomOne.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4071,7 +4300,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>1710645772</v>
+        <v>1713202791</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -4085,6 +4314,7 @@
         </is>
       </c>
       <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4103,7 +4333,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>1710651879</v>
+        <v>1713212389</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -4113,10 +4343,15 @@
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Temperature.state: Comfortable</t>
+          <t>MeetingRoomOne.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4135,7 +4370,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>1710653623</v>
+        <v>1713226376</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -4149,6 +4384,7 @@
         </is>
       </c>
       <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4167,7 +4403,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>1710654481</v>
+        <v>1713228714</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -4181,6 +4417,11 @@
         </is>
       </c>
       <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4199,7 +4440,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>1710659714</v>
+        <v>1713231615</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -4213,6 +4454,7 @@
         </is>
       </c>
       <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4231,7 +4473,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>1710660589</v>
+        <v>1713241412</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -4245,6 +4487,11 @@
         </is>
       </c>
       <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4263,7 +4510,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>1710722893</v>
+        <v>1713245810</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -4277,6 +4524,7 @@
         </is>
       </c>
       <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4295,7 +4543,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>1710723767</v>
+        <v>1713246713</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -4309,6 +4557,11 @@
         </is>
       </c>
       <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4327,7 +4580,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>1710728626</v>
+        <v>1713286152</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -4341,6 +4594,7 @@
         </is>
       </c>
       <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4359,7 +4613,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>1710733860</v>
+        <v>1713286982</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -4369,10 +4623,15 @@
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Temperature.state: Comfortable</t>
+          <t>MeetingRoomOne.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4391,7 +4650,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>1710785548</v>
+        <v>1713313889</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -4405,6 +4664,7 @@
         </is>
       </c>
       <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4423,7 +4683,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>1710794808</v>
+        <v>1713314662</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -4437,6 +4697,11 @@
         </is>
       </c>
       <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4455,7 +4720,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>1710812215</v>
+        <v>1713318274</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -4469,6 +4734,7 @@
         </is>
       </c>
       <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4487,7 +4753,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>1710813827</v>
+        <v>1713326677</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -4497,10 +4763,11 @@
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Temperature.state: ExcessivelyCold</t>
+          <t>MeetingRoomOne.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4519,7 +4786,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>1710818119</v>
+        <v>1713378028</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -4533,6 +4800,7 @@
         </is>
       </c>
       <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4551,7 +4819,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>1710822806</v>
+        <v>1713387777</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -4561,10 +4829,15 @@
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Temperature.state: Comfortable</t>
+          <t>MeetingRoomOne.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4583,7 +4856,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>1710825312</v>
+        <v>1713402866</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -4597,6 +4870,7 @@
         </is>
       </c>
       <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4615,7 +4889,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>1710826249</v>
+        <v>1713403634</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -4629,6 +4903,11 @@
         </is>
       </c>
       <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4647,7 +4926,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>1710830872</v>
+        <v>1713406831</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -4661,6 +4940,7 @@
         </is>
       </c>
       <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4679,7 +4959,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>1710831779</v>
+        <v>1713415744</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -4689,10 +4969,11 @@
       <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Temperature.state: ExcessivelyCold</t>
+          <t>MeetingRoomOne.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4711,7 +4992,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>1710871878</v>
+        <v>1713461523</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -4725,6 +5006,7 @@
         </is>
       </c>
       <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4743,7 +5025,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>1710872704</v>
+        <v>1713470613</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -4757,6 +5039,11 @@
         </is>
       </c>
       <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4775,7 +5062,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>1710882775</v>
+        <v>1713488323</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -4789,6 +5076,7 @@
         </is>
       </c>
       <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4807,7 +5095,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>1710883621</v>
+        <v>1713493530</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -4817,10 +5105,11 @@
       <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Temperature.state: ExcessivelyCold</t>
+          <t>MeetingRoomOne.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4839,7 +5128,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>1710891616</v>
+        <v>1713502467</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -4853,6 +5142,7 @@
         </is>
       </c>
       <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4871,7 +5161,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>1710892536</v>
+        <v>1713503310</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
@@ -4885,6 +5175,11 @@
         </is>
       </c>
       <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4903,7 +5198,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>1710895767</v>
+        <v>1713545380</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
@@ -4917,6 +5212,7 @@
         </is>
       </c>
       <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4935,7 +5231,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>1710896789</v>
+        <v>1713546188</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -4949,6 +5245,11 @@
         </is>
       </c>
       <c r="H141" t="inlineStr"/>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4967,7 +5268,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>1710899262</v>
+        <v>1713576628</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -4981,6 +5282,7 @@
         </is>
       </c>
       <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -4999,7 +5301,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>1710900373</v>
+        <v>1713577467</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
@@ -5013,6 +5315,11 @@
         </is>
       </c>
       <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5031,7 +5338,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>1710902897</v>
+        <v>1713582091</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
@@ -5045,6 +5352,7 @@
         </is>
       </c>
       <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5063,7 +5371,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>1710904038</v>
+        <v>1713582951</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
@@ -5077,6 +5385,11 @@
         </is>
       </c>
       <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5095,7 +5408,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>1710906509</v>
+        <v>1713586061</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
@@ -5109,6 +5422,7 @@
         </is>
       </c>
       <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5127,7 +5441,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>1710907582</v>
+        <v>1713586918</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
@@ -5141,6 +5455,11 @@
         </is>
       </c>
       <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -5159,7 +5478,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>1710910003</v>
+        <v>1713590078</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
@@ -5173,6 +5492,7 @@
         </is>
       </c>
       <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5191,7 +5511,7 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>1710911085</v>
+        <v>1713590995</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
@@ -5205,6 +5525,11 @@
         </is>
       </c>
       <c r="H149" t="inlineStr"/>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -5223,7 +5548,7 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>1710913531</v>
+        <v>1713594631</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
@@ -5237,6 +5562,7 @@
         </is>
       </c>
       <c r="H150" t="inlineStr"/>
+      <c r="I150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -5255,7 +5581,7 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>1710914709</v>
+        <v>1713595474</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
@@ -5269,6 +5595,11 @@
         </is>
       </c>
       <c r="H151" t="inlineStr"/>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -5287,7 +5618,7 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>1710917168</v>
+        <v>1713629081</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
@@ -5301,6 +5632,7 @@
         </is>
       </c>
       <c r="H152" t="inlineStr"/>
+      <c r="I152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -5319,7 +5651,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>1710918315</v>
+        <v>1713629922</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
@@ -5333,6 +5665,11 @@
         </is>
       </c>
       <c r="H153" t="inlineStr"/>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -5351,7 +5688,7 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>1710920724</v>
+        <v>1713662105</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
@@ -5365,6 +5702,7 @@
         </is>
       </c>
       <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -5383,7 +5721,7 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>1710921731</v>
+        <v>1713662966</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
@@ -5397,6 +5735,11 @@
         </is>
       </c>
       <c r="H155" t="inlineStr"/>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -5415,7 +5758,7 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>1710924979</v>
+        <v>1713667621</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
@@ -5429,6 +5772,7 @@
         </is>
       </c>
       <c r="H156" t="inlineStr"/>
+      <c r="I156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -5447,7 +5791,7 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>1710925965</v>
+        <v>1713668460</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
@@ -5461,6 +5805,11 @@
         </is>
       </c>
       <c r="H157" t="inlineStr"/>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -5479,7 +5828,7 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>1710929824</v>
+        <v>1713672138</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
@@ -5493,6 +5842,7 @@
         </is>
       </c>
       <c r="H158" t="inlineStr"/>
+      <c r="I158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -5511,7 +5861,7 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>1710951141</v>
+        <v>1713673066</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
@@ -5525,6 +5875,11 @@
         </is>
       </c>
       <c r="H159" t="inlineStr"/>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -5543,7 +5898,7 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>1710956684</v>
+        <v>1713677173</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
@@ -5557,6 +5912,7 @@
         </is>
       </c>
       <c r="H160" t="inlineStr"/>
+      <c r="I160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -5575,7 +5931,7 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>1710957475</v>
+        <v>1713678048</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
@@ -5589,6 +5945,11 @@
         </is>
       </c>
       <c r="H161" t="inlineStr"/>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -5607,7 +5968,7 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>1710967325</v>
+        <v>1713683494</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
@@ -5621,6 +5982,7 @@
         </is>
       </c>
       <c r="H162" t="inlineStr"/>
+      <c r="I162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -5639,7 +6001,7 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>1710968143</v>
+        <v>1713684274</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
@@ -5653,6 +6015,11 @@
         </is>
       </c>
       <c r="H163" t="inlineStr"/>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -5671,7 +6038,7 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>1710977921</v>
+        <v>1713745458</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
@@ -5685,6 +6052,7 @@
         </is>
       </c>
       <c r="H164" t="inlineStr"/>
+      <c r="I164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -5703,7 +6071,7 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>1710978787</v>
+        <v>1713746242</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
@@ -5717,6 +6085,11 @@
         </is>
       </c>
       <c r="H165" t="inlineStr"/>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -5735,7 +6108,7 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>1710984248</v>
+        <v>1713750442</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
@@ -5749,6 +6122,7 @@
         </is>
       </c>
       <c r="H166" t="inlineStr"/>
+      <c r="I166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -5767,7 +6141,7 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>1710985243</v>
+        <v>1713754778</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
@@ -5777,10 +6151,11 @@
       <c r="F167" t="inlineStr"/>
       <c r="G167" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Temperature.state: ExcessivelyCold</t>
+          <t>MeetingRoomOne.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H167" t="inlineStr"/>
+      <c r="I167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -5799,7 +6174,7 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>1710988505</v>
+        <v>1713812624</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
@@ -5813,6 +6188,7 @@
         </is>
       </c>
       <c r="H168" t="inlineStr"/>
+      <c r="I168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -5831,7 +6207,7 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>1710989489</v>
+        <v>1713821601</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
@@ -5845,6 +6221,11 @@
         </is>
       </c>
       <c r="H169" t="inlineStr"/>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -5863,7 +6244,7 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>1710992732</v>
+        <v>1713830651</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
@@ -5877,6 +6258,7 @@
         </is>
       </c>
       <c r="H170" t="inlineStr"/>
+      <c r="I170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -5895,7 +6277,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>1710993697</v>
+        <v>1713830957</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
@@ -5905,10 +6287,11 @@
       <c r="F171" t="inlineStr"/>
       <c r="G171" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Temperature.state: ExcessivelyCold</t>
+          <t>MeetingRoomOne.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H171" t="inlineStr"/>
+      <c r="I171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -5927,7 +6310,7 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>1710996332</v>
+        <v>1713831521</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
@@ -5937,10 +6320,11 @@
       <c r="F172" t="inlineStr"/>
       <c r="G172" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Temperature.state: Cold</t>
+          <t>MeetingRoomOne.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H172" t="inlineStr"/>
+      <c r="I172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -5959,7 +6343,7 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>1710997422</v>
+        <v>1713834638</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
@@ -5969,10 +6353,11 @@
       <c r="F173" t="inlineStr"/>
       <c r="G173" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Temperature.state: ExcessivelyCold</t>
+          <t>MeetingRoomOne.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H173" t="inlineStr"/>
+      <c r="I173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -5991,7 +6376,7 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>1710999886</v>
+        <v>1713891856</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
@@ -6005,6 +6390,7 @@
         </is>
       </c>
       <c r="H174" t="inlineStr"/>
+      <c r="I174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -6023,7 +6409,7 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>1711000965</v>
+        <v>1713901062</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
@@ -6037,6 +6423,11 @@
         </is>
       </c>
       <c r="H175" t="inlineStr"/>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -6055,7 +6446,7 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>1711003333</v>
+        <v>1713920193</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
@@ -6069,6 +6460,7 @@
         </is>
       </c>
       <c r="H176" t="inlineStr"/>
+      <c r="I176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -6087,7 +6479,7 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>1711004457</v>
+        <v>1713921223</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
@@ -6101,6 +6493,11 @@
         </is>
       </c>
       <c r="H177" t="inlineStr"/>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -6119,7 +6516,7 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>1711006884</v>
+        <v>1713926011</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
@@ -6133,6 +6530,7 @@
         </is>
       </c>
       <c r="H178" t="inlineStr"/>
+      <c r="I178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -6151,7 +6549,7 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>1711007964</v>
+        <v>1713927979</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
@@ -6161,10 +6559,11 @@
       <c r="F179" t="inlineStr"/>
       <c r="G179" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Temperature.state: ExcessivelyCold</t>
+          <t>MeetingRoomOne.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H179" t="inlineStr"/>
+      <c r="I179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -6183,7 +6582,7 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>1711011180</v>
+        <v>1713986618</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
@@ -6197,6 +6596,7 @@
         </is>
       </c>
       <c r="H180" t="inlineStr"/>
+      <c r="I180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -6215,7 +6615,7 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>1711012139</v>
+        <v>1713996100</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
@@ -6229,6 +6629,11 @@
         </is>
       </c>
       <c r="H181" t="inlineStr"/>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -6247,7 +6652,7 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>1711015344</v>
+        <v>1714004017</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
@@ -6261,6 +6666,7 @@
         </is>
       </c>
       <c r="H182" t="inlineStr"/>
+      <c r="I182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -6279,7 +6685,7 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>1711016215</v>
+        <v>1714010712</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
@@ -6293,6 +6699,11 @@
         </is>
       </c>
       <c r="H183" t="inlineStr"/>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -6311,7 +6722,7 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>1711040571</v>
+        <v>1714015357</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
@@ -6325,6 +6736,7 @@
         </is>
       </c>
       <c r="H184" t="inlineStr"/>
+      <c r="I184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -6343,7 +6755,7 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>1711041450</v>
+        <v>1714017994</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
@@ -6357,6 +6769,11 @@
         </is>
       </c>
       <c r="H185" t="inlineStr"/>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -6375,7 +6792,7 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>1711047184</v>
+        <v>1714063707</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
@@ -6389,6 +6806,7 @@
         </is>
       </c>
       <c r="H186" t="inlineStr"/>
+      <c r="I186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -6407,7 +6825,7 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>1711048000</v>
+        <v>1714064652</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
@@ -6421,6 +6839,11 @@
         </is>
       </c>
       <c r="H187" t="inlineStr"/>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -6439,7 +6862,7 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>1711057700</v>
+        <v>1714093474</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
@@ -6453,6 +6876,7 @@
         </is>
       </c>
       <c r="H188" t="inlineStr"/>
+      <c r="I188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -6471,7 +6895,7 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>1711058509</v>
+        <v>1714096449</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
@@ -6485,6 +6909,11 @@
         </is>
       </c>
       <c r="H189" t="inlineStr"/>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -6503,7 +6932,7 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>1711067600</v>
+        <v>1714098232</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
@@ -6517,6 +6946,7 @@
         </is>
       </c>
       <c r="H190" t="inlineStr"/>
+      <c r="I190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -6535,7 +6965,7 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>1711072138</v>
+        <v>1714105720</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
@@ -6549,6 +6979,11 @@
         </is>
       </c>
       <c r="H191" t="inlineStr"/>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -6567,7 +7002,7 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>1711075461</v>
+        <v>1714149668</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
@@ -6581,6 +7016,7 @@
         </is>
       </c>
       <c r="H192" t="inlineStr"/>
+      <c r="I192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -6599,7 +7035,7 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>1711080467</v>
+        <v>1714150502</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
@@ -6609,10 +7045,15 @@
       <c r="F193" t="inlineStr"/>
       <c r="G193" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Temperature.state: Comfortable</t>
+          <t>MeetingRoomOne.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H193" t="inlineStr"/>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -6631,7 +7072,7 @@
         </is>
       </c>
       <c r="D194" t="n">
-        <v>1711089649</v>
+        <v>1714181120</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
@@ -6641,10 +7082,11 @@
       <c r="F194" t="inlineStr"/>
       <c r="G194" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Temperature.state: Warm</t>
+          <t>MeetingRoomOne.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H194" t="inlineStr"/>
+      <c r="I194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -6663,7 +7105,7 @@
         </is>
       </c>
       <c r="D195" t="n">
-        <v>1711129267</v>
+        <v>1714181960</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
@@ -6673,10 +7115,15 @@
       <c r="F195" t="inlineStr"/>
       <c r="G195" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Temperature.state: Comfortable</t>
+          <t>MeetingRoomOne.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H195" t="inlineStr"/>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -6695,7 +7142,7 @@
         </is>
       </c>
       <c r="D196" t="n">
-        <v>1711138520</v>
+        <v>1714186514</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
@@ -6709,6 +7156,7 @@
         </is>
       </c>
       <c r="H196" t="inlineStr"/>
+      <c r="I196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -6727,7 +7175,7 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>1711156892</v>
+        <v>1714187408</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
@@ -6737,10 +7185,15 @@
       <c r="F197" t="inlineStr"/>
       <c r="G197" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Temperature.state: Comfortable</t>
+          <t>MeetingRoomOne.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H197" t="inlineStr"/>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -6759,7 +7212,7 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>1711162930</v>
+        <v>1714190536</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
@@ -6773,6 +7226,7 @@
         </is>
       </c>
       <c r="H198" t="inlineStr"/>
+      <c r="I198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -6791,7 +7245,7 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>1711164017</v>
+        <v>1714191481</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
@@ -6805,6 +7259,11 @@
         </is>
       </c>
       <c r="H199" t="inlineStr"/>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -6823,7 +7282,7 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>1711166417</v>
+        <v>1714194602</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
@@ -6837,6 +7296,7 @@
         </is>
       </c>
       <c r="H200" t="inlineStr"/>
+      <c r="I200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -6855,7 +7315,7 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>1711169600</v>
+        <v>1714195545</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
@@ -6865,10 +7325,15 @@
       <c r="F201" t="inlineStr"/>
       <c r="G201" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Temperature.state: Comfortable</t>
+          <t>MeetingRoomOne.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H201" t="inlineStr"/>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -6887,7 +7352,7 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>1711176629</v>
+        <v>1714198762</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
@@ -6897,10 +7362,11 @@
       <c r="F202" t="inlineStr"/>
       <c r="G202" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Temperature.state: Warm</t>
+          <t>MeetingRoomOne.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H202" t="inlineStr"/>
+      <c r="I202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -6919,7 +7385,7 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>1711215682</v>
+        <v>1714199698</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
@@ -6929,10 +7395,15 @@
       <c r="F203" t="inlineStr"/>
       <c r="G203" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Temperature.state: Comfortable</t>
+          <t>MeetingRoomOne.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H203" t="inlineStr"/>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -6951,7 +7422,7 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>1711225633</v>
+        <v>1714204433</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
@@ -6965,6 +7436,7 @@
         </is>
       </c>
       <c r="H204" t="inlineStr"/>
+      <c r="I204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -6983,7 +7455,7 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>1711240802</v>
+        <v>1714205302</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
@@ -6997,6 +7469,11 @@
         </is>
       </c>
       <c r="H205" t="inlineStr"/>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -7015,7 +7492,7 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>1711244147</v>
+        <v>1714264649</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
@@ -7029,6 +7506,7 @@
         </is>
       </c>
       <c r="H206" t="inlineStr"/>
+      <c r="I206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -7047,7 +7525,7 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>1711257051</v>
+        <v>1714265499</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
@@ -7057,10 +7535,15 @@
       <c r="F207" t="inlineStr"/>
       <c r="G207" t="inlineStr">
         <is>
-          <t>MeetingRoomOne.Temperature.state: Comfortable</t>
+          <t>MeetingRoomOne.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H207" t="inlineStr"/>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -7079,7 +7562,7 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>1711303309</v>
+        <v>1714270230</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
@@ -7093,6 +7576,7 @@
         </is>
       </c>
       <c r="H208" t="inlineStr"/>
+      <c r="I208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -7111,7 +7595,7 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>1711312944</v>
+        <v>1714271030</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
@@ -7125,6 +7609,11 @@
         </is>
       </c>
       <c r="H209" t="inlineStr"/>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -7143,7 +7632,7 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>1711329898</v>
+        <v>1714275277</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
@@ -7157,6 +7646,7 @@
         </is>
       </c>
       <c r="H210" t="inlineStr"/>
+      <c r="I210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -7175,7 +7665,7 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>1711336040</v>
+        <v>1714276160</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
@@ -7189,6 +7679,11 @@
         </is>
       </c>
       <c r="H211" t="inlineStr"/>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -7207,7 +7702,7 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>1711339300</v>
+        <v>1714279338</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
@@ -7221,6 +7716,7 @@
         </is>
       </c>
       <c r="H212" t="inlineStr"/>
+      <c r="I212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -7239,7 +7735,7 @@
         </is>
       </c>
       <c r="D213" t="n">
-        <v>1711343643</v>
+        <v>1714280237</v>
       </c>
       <c r="E213" t="inlineStr">
         <is>
@@ -7253,6 +7749,11 @@
         </is>
       </c>
       <c r="H213" t="inlineStr"/>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -7271,7 +7772,7 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>1711348456</v>
+        <v>1714283557</v>
       </c>
       <c r="E214" t="inlineStr">
         <is>
@@ -7285,6 +7786,7 @@
         </is>
       </c>
       <c r="H214" t="inlineStr"/>
+      <c r="I214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -7303,7 +7805,7 @@
         </is>
       </c>
       <c r="D215" t="n">
-        <v>1711349342</v>
+        <v>1714284430</v>
       </c>
       <c r="E215" t="inlineStr">
         <is>
@@ -7317,6 +7819,11 @@
         </is>
       </c>
       <c r="H215" t="inlineStr"/>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -7335,7 +7842,7 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>1711414400</v>
+        <v>1714288574</v>
       </c>
       <c r="E216" t="inlineStr">
         <is>
@@ -7349,6 +7856,7 @@
         </is>
       </c>
       <c r="H216" t="inlineStr"/>
+      <c r="I216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -7367,7 +7875,7 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>1711418200</v>
+        <v>1714289429</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
@@ -7381,454 +7889,11 @@
         </is>
       </c>
       <c r="H217" t="inlineStr"/>
-    </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne</t>
-        </is>
-      </c>
-      <c r="D218" t="n">
-        <v>1711422646</v>
-      </c>
-      <c r="E218" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F218" t="inlineStr"/>
-      <c r="G218" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne.Temperature.state: Cold</t>
-        </is>
-      </c>
-      <c r="H218" t="inlineStr"/>
-    </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne</t>
-        </is>
-      </c>
-      <c r="D219" t="n">
-        <v>1711427494</v>
-      </c>
-      <c r="E219" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F219" t="inlineStr"/>
-      <c r="G219" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne.Temperature.state: Comfortable</t>
-        </is>
-      </c>
-      <c r="H219" t="inlineStr"/>
-    </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne</t>
-        </is>
-      </c>
-      <c r="D220" t="n">
-        <v>1711476904</v>
-      </c>
-      <c r="E220" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F220" t="inlineStr"/>
-      <c r="G220" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne.Temperature.state: Cold</t>
-        </is>
-      </c>
-      <c r="H220" t="inlineStr"/>
-    </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne</t>
-        </is>
-      </c>
-      <c r="D221" t="n">
-        <v>1711486065</v>
-      </c>
-      <c r="E221" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F221" t="inlineStr"/>
-      <c r="G221" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne.Temperature.state: ExcessivelyCold</t>
-        </is>
-      </c>
-      <c r="H221" t="inlineStr"/>
-    </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C222" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne</t>
-        </is>
-      </c>
-      <c r="D222" t="n">
-        <v>1711505681</v>
-      </c>
-      <c r="E222" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F222" t="inlineStr"/>
-      <c r="G222" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne.Temperature.state: Cold</t>
-        </is>
-      </c>
-      <c r="H222" t="inlineStr"/>
-    </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C223" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne</t>
-        </is>
-      </c>
-      <c r="D223" t="n">
-        <v>1711513773</v>
-      </c>
-      <c r="E223" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F223" t="inlineStr"/>
-      <c r="G223" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne.Temperature.state: Comfortable</t>
-        </is>
-      </c>
-      <c r="H223" t="inlineStr"/>
-    </row>
-    <row r="224">
-      <c r="A224" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C224" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne</t>
-        </is>
-      </c>
-      <c r="D224" t="n">
-        <v>1711522934</v>
-      </c>
-      <c r="E224" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F224" t="inlineStr"/>
-      <c r="G224" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne.Temperature.state: Warm</t>
-        </is>
-      </c>
-      <c r="H224" t="inlineStr"/>
-    </row>
-    <row r="225">
-      <c r="A225" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C225" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne</t>
-        </is>
-      </c>
-      <c r="D225" t="n">
-        <v>1711555343</v>
-      </c>
-      <c r="E225" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F225" t="inlineStr"/>
-      <c r="G225" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne.Temperature.state: Comfortable</t>
-        </is>
-      </c>
-      <c r="H225" t="inlineStr"/>
-    </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C226" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne</t>
-        </is>
-      </c>
-      <c r="D226" t="n">
-        <v>1711562391</v>
-      </c>
-      <c r="E226" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F226" t="inlineStr"/>
-      <c r="G226" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne.Temperature.state: Cold</t>
-        </is>
-      </c>
-      <c r="H226" t="inlineStr"/>
-    </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne</t>
-        </is>
-      </c>
-      <c r="D227" t="n">
-        <v>1711571590</v>
-      </c>
-      <c r="E227" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F227" t="inlineStr"/>
-      <c r="G227" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne.Temperature.state: ExcessivelyCold</t>
-        </is>
-      </c>
-      <c r="H227" t="inlineStr"/>
-    </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C228" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne</t>
-        </is>
-      </c>
-      <c r="D228" t="n">
-        <v>1711592651</v>
-      </c>
-      <c r="E228" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F228" t="inlineStr"/>
-      <c r="G228" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne.Temperature.state: Cold</t>
-        </is>
-      </c>
-      <c r="H228" t="inlineStr"/>
-    </row>
-    <row r="229">
-      <c r="A229" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C229" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne</t>
-        </is>
-      </c>
-      <c r="D229" t="n">
-        <v>1711601326</v>
-      </c>
-      <c r="E229" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F229" t="inlineStr"/>
-      <c r="G229" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne.Temperature.state: Comfortable</t>
-        </is>
-      </c>
-      <c r="H229" t="inlineStr"/>
-    </row>
-    <row r="230">
-      <c r="A230" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C230" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne</t>
-        </is>
-      </c>
-      <c r="D230" t="n">
-        <v>1711610646</v>
-      </c>
-      <c r="E230" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F230" t="inlineStr"/>
-      <c r="G230" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne.Temperature.state: Warm</t>
-        </is>
-      </c>
-      <c r="H230" t="inlineStr"/>
-    </row>
-    <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C231" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne</t>
-        </is>
-      </c>
-      <c r="D231" t="n">
-        <v>1711621335</v>
-      </c>
-      <c r="E231" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F231" t="inlineStr"/>
-      <c r="G231" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne.Temperature.state: Comfortable</t>
-        </is>
-      </c>
-      <c r="H231" t="inlineStr"/>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
